--- a/templates/inventory_template_1.xlsx
+++ b/templates/inventory_template_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mickey_wang/Workspace/pdf_invoice_parser/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE24451-F68D-634D-9645-9B7951D63A18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C849CF21-F853-2444-BE98-6980260B11C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13780" yWindow="4300" windowWidth="27840" windowHeight="16940" xr2:uid="{B46F508C-1DBE-8841-ACEE-DE903A2297B3}"/>
+    <workbookView xWindow="7660" yWindow="2360" windowWidth="27840" windowHeight="16940" xr2:uid="{B46F508C-1DBE-8841-ACEE-DE903A2297B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
+    <t>浙江大学科研材料入库单（仓库联）</t>
+  </si>
+  <si>
     <t xml:space="preserve">项目（课题）名称及代码：                              </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -83,10 +86,6 @@
   </si>
   <si>
     <t>②出入库保管需为同一人，指定专人负责；采购、验收保管不能为同一人。</t>
-  </si>
-  <si>
-    <t>浙江大学科研材料入库单（财务记账联）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -96,7 +95,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -140,6 +139,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -149,7 +155,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -158,71 +164,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -230,23 +181,8 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -257,64 +193,49 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,252 +551,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D3BD497-1FB3-AC47-B44C-4AF0A1860B76}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19">
-      <c r="A1" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-    </row>
-    <row r="2" spans="1:9" ht="17" thickBot="1">
-      <c r="A2" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="1"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
+      <c r="B3" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="11" t="s">
         <v>5</v>
       </c>
+      <c r="E3" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="F3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="18" t="s">
         <v>7</v>
       </c>
+      <c r="G3" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="H3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="18" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="17" thickBot="1">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="4" t="s">
+      <c r="I3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="4" t="s">
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="4" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="1:9" ht="17" thickBot="1">
-      <c r="A5" s="5"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="7"/>
+      <c r="H5" s="5"/>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="17" thickBot="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="7"/>
+    <row r="6" spans="1:9">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="5"/>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="17" thickBot="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" ht="17" thickBot="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+    <row r="7" spans="1:9">
+      <c r="A7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" ht="17" thickBot="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" ht="17" thickBot="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" ht="17" thickBot="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" ht="17" thickBot="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" ht="17" thickBot="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" ht="17" thickBot="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:9" ht="17" thickBot="1">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" ht="17" customHeight="1" thickBot="1">
-      <c r="A16" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="16"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="10"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A16:I16"/>
+  <mergeCells count="14">
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -883,6 +713,10 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/inventory_template_1.xlsx
+++ b/templates/inventory_template_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mickey_wang/Workspace/pdf_invoice_parser/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C849CF21-F853-2444-BE98-6980260B11C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DA08AD-D55D-6D43-B63D-CFBD42860AC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7660" yWindow="2360" windowWidth="27840" windowHeight="16940" xr2:uid="{B46F508C-1DBE-8841-ACEE-DE903A2297B3}"/>
   </bookViews>
@@ -193,7 +193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -235,6 +235,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -571,10 +574,10 @@
       <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
